--- a/utils/Tools/excel/21_condition_条件.xlsx
+++ b/utils/Tools/excel/21_condition_条件.xlsx
@@ -150,7 +150,7 @@
     <t>[]{int op;int target}</t>
   </si>
   <si>
-    <t>s</t>
+    <t>cs</t>
   </si>
 </sst>
 </file>
@@ -316,12 +316,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
